--- a/www/download/IND.surplus_value.empe.r.pc.rpO2.xlsx
+++ b/www/download/IND.surplus_value.empe.r.pc.rpO2.xlsx
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Ochoa 2</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -673,7 +678,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Austrália</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -683,84 +688,84 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-83.17</t>
+          <t>-0.831740976401443</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>-83.86</t>
+          <t>-0.838601742473443</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>-78.88</t>
+          <t>-0.788815481421025</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-79.77</t>
+          <t>-0.797689714997167</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-87.24</t>
+          <t>-0.87236617685789</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-89.85</t>
+          <t>-0.898484112822641</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-88.65</t>
+          <t>-0.886503719431654</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-90.4</t>
+          <t>-0.903968892131985</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>-90.56</t>
+          <t>-0.905574598747295</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-87.24</t>
+          <t>-0.872356665152105</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>-91.69</t>
+          <t>-0.916896721847011</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>-92.21</t>
+          <t>-0.922085416244953</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-92.49</t>
+          <t>-0.924892286891953</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-91.53</t>
+          <t>-0.91527873314475</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-88.38</t>
+          <t>-0.883762443704321</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Áustria</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -770,84 +775,84 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-84.11</t>
+          <t>-0.841101904850591</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>-84.87</t>
+          <t>-0.84865441629732</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>-77.51</t>
+          <t>-0.775117591135447</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-79.79</t>
+          <t>-0.797896452826566</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-84.42</t>
+          <t>-0.844150138261485</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-88.14</t>
+          <t>-0.8813889931307</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-89.21</t>
+          <t>-0.892135513519011</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-89.1</t>
+          <t>-0.890971170427799</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>-89.2</t>
+          <t>-0.891995869851693</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-89.13</t>
+          <t>-0.891318423054188</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>-90.82</t>
+          <t>-0.908158208898466</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>-91.73</t>
+          <t>-0.917309161559101</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>-89.82</t>
+          <t>-0.898185284538602</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>-88.79</t>
+          <t>-0.887898315376422</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>-84.1</t>
+          <t>-0.841006001153677</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Bélgica</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -857,84 +862,84 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-80.82</t>
+          <t>-0.808187904307257</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>-78.03</t>
+          <t>-0.780252580050876</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>-71.86</t>
+          <t>-0.718637427064838</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-73.4</t>
+          <t>-0.734028833797128</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-78.84</t>
+          <t>-0.788411611881746</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-85.16</t>
+          <t>-0.851561244367653</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-85.82</t>
+          <t>-0.858213625632731</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-87.31</t>
+          <t>-0.873059865850377</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>-88.9</t>
+          <t>-0.889009216256148</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-88.83</t>
+          <t>-0.888275780651813</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>-90.72</t>
+          <t>-0.907155794902085</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>-90.16</t>
+          <t>-0.901571787086369</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>-87.89</t>
+          <t>-0.878943823434686</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>-87.93</t>
+          <t>-0.879314216252301</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>-84.12</t>
+          <t>-0.84118498176207</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -944,84 +949,84 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>26.27</t>
+          <t>0.262701093893218</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>49.31</t>
+          <t>0.493065461170718</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>119.14</t>
+          <t>1.19139008097145</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>61.45</t>
+          <t>0.614480844734389</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>35.21</t>
+          <t>0.352084159782855</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>13.83</t>
+          <t>0.138273137977847</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-1.09</t>
+          <t>-0.0108573251130638</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-14.65</t>
+          <t>-0.146536860938935</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>-30.65</t>
+          <t>-0.306510614784757</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-38.71</t>
+          <t>-0.387051476201445</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>-43.63</t>
+          <t>-0.436282258661218</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>-51.64</t>
+          <t>-0.516399332298636</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>-46.61</t>
+          <t>-0.466138853483784</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>-39.95</t>
+          <t>-0.399539379635433</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>-30.11</t>
+          <t>-0.301112745489694</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1031,84 +1036,84 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>151.71</t>
+          <t>1.51709157534113</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>148.92</t>
+          <t>1.48920667473864</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>168.42</t>
+          <t>1.68418675282418</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>155.41</t>
+          <t>1.55414124401596</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>159.85</t>
+          <t>1.5984998794691</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>74.64</t>
+          <t>0.746396583820014</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>67.37</t>
+          <t>0.673695153569632</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>89.5</t>
+          <t>0.894978485273946</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>83.5</t>
+          <t>0.834967031257527</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>63.62</t>
+          <t>0.636152643601029</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>49.59</t>
+          <t>0.495864385648551</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>39.9</t>
+          <t>0.399019786165701</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>46.63</t>
+          <t>0.466262284566219</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>38.47</t>
+          <t>0.38472343879412</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>85.79</t>
+          <t>0.857873870616867</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Canadá</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1118,84 +1123,84 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-62.83</t>
+          <t>-0.628281046969543</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>-63.23</t>
+          <t>-0.63229097755291</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>-58.92</t>
+          <t>-0.589170443426242</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-64.74</t>
+          <t>-0.647426657492407</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-72.05</t>
+          <t>-0.720507281072974</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-82.71</t>
+          <t>-0.827109240658976</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-84.16</t>
+          <t>-0.841616212883297</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-82.02</t>
+          <t>-0.820163552821933</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>-83.36</t>
+          <t>-0.833584505369663</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-82.94</t>
+          <t>-0.829371346461096</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>-86.74</t>
+          <t>-0.867436149481802</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>-86.02</t>
+          <t>-0.860158073502598</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>-82.79</t>
+          <t>-0.82787204806543</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>-81.41</t>
+          <t>-0.814063421866122</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>-74.69</t>
+          <t>-0.746946276027141</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1205,84 +1210,84 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-27.26</t>
+          <t>-0.272571476220398</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>-25.42</t>
+          <t>-0.254249594922908</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>-21.05</t>
+          <t>-0.210507505620771</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-17.65</t>
+          <t>-0.176522781202169</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-15.27</t>
+          <t>-0.152658619358954</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>-16.65</t>
+          <t>-0.166467029692031</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-10.24</t>
+          <t>-0.102420154144871</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-5.18</t>
+          <t>-0.0517948403318355</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>-0.00950905010364611</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.00558313530399746</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2.72</t>
+          <t>0.0272011947957602</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>5.43</t>
+          <t>0.0543114666903566</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>19.46</t>
+          <t>0.194578273471636</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>19.82</t>
+          <t>0.198193528103279</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>29.76</t>
+          <t>0.297631293140206</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Chipre</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1292,84 +1297,84 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-59.17</t>
+          <t>-0.591703837757172</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>-65.45</t>
+          <t>-0.654535743727292</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>-43.52</t>
+          <t>-0.435227509137359</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>-53.07</t>
+          <t>-0.530680771844629</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-70.3</t>
+          <t>-0.703011811517367</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-76.99</t>
+          <t>-0.769859786995912</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-79.7</t>
+          <t>-0.797002258201689</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-80.69</t>
+          <t>-0.80686873734643</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>-80.83</t>
+          <t>-0.808326643612413</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>-78.57</t>
+          <t>-0.785733072458379</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>-73.06</t>
+          <t>-0.730564815559781</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>-68.13</t>
+          <t>-0.681253857993906</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>-64.55</t>
+          <t>-0.645545615983394</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>-58.5</t>
+          <t>-0.584963510896054</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>-20.95</t>
+          <t>-0.209523886375446</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>República Tcheca</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1379,84 +1384,84 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-4.4</t>
+          <t>-0.0439894263670542</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>-45.33</t>
+          <t>-0.453266536886088</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>-18.66</t>
+          <t>-0.186591199490589</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>-32.72</t>
+          <t>-0.327246373416444</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-47.61</t>
+          <t>-0.476146225947766</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-60.51</t>
+          <t>-0.605064511510582</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-71.23</t>
+          <t>-0.712252388964224</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-73.54</t>
+          <t>-0.735363554433835</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>-76.52</t>
+          <t>-0.765167241002678</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>-76.25</t>
+          <t>-0.762489314771916</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>-80.16</t>
+          <t>-0.801635987642704</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>-80.41</t>
+          <t>-0.804090707133617</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>-75.79</t>
+          <t>-0.757908691228623</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>-73.19</t>
+          <t>-0.731922220407183</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>-54.9</t>
+          <t>-0.548966965368906</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Alemanha</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1466,84 +1471,84 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-87.81</t>
+          <t>-0.878146455912016</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>-86.36</t>
+          <t>-0.863551400958544</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>-83.98</t>
+          <t>-0.83978190711005</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-85.5</t>
+          <t>-0.854968204008819</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-88.9</t>
+          <t>-0.888966720277939</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-92.18</t>
+          <t>-0.92176702613672</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-93.05</t>
+          <t>-0.930476095896861</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-93.12</t>
+          <t>-0.931200826269452</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>-93.58</t>
+          <t>-0.935770874319108</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>-93.22</t>
+          <t>-0.932238356801039</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>-93.65</t>
+          <t>-0.936478899187944</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>-94.04</t>
+          <t>-0.940353313824892</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>-92.45</t>
+          <t>-0.924507630578499</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>-91.63</t>
+          <t>-0.916345613215632</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>-88.31</t>
+          <t>-0.88309082505282</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Dinamarca</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1553,84 +1558,84 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-91.75</t>
+          <t>-0.917464598569614</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>-91.29</t>
+          <t>-0.912941238403055</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>-87.45</t>
+          <t>-0.874547483772435</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>-88.25</t>
+          <t>-0.882499644962828</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-89.61</t>
+          <t>-0.896111059938636</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-91.1</t>
+          <t>-0.910974795694859</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-91.83</t>
+          <t>-0.918323306871083</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-92.37</t>
+          <t>-0.923674747365266</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>-93.05</t>
+          <t>-0.930468601213036</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>-93.23</t>
+          <t>-0.932259544921366</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>-93.9</t>
+          <t>-0.939029912692993</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>-93.73</t>
+          <t>-0.937252007570364</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>-92.57</t>
+          <t>-0.925733388826762</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>-93.15</t>
+          <t>-0.931537793323359</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>-88.43</t>
+          <t>-0.884294894674597</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Espanha</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1640,84 +1645,84 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-72.18</t>
+          <t>-0.721763837117764</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>-72.91</t>
+          <t>-0.729138574392902</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>-67.89</t>
+          <t>-0.678949562905883</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>-70.57</t>
+          <t>-0.705730453213997</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-78.9</t>
+          <t>-0.788982654046232</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-86.08</t>
+          <t>-0.860802945277815</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-86.8</t>
+          <t>-0.868032825929921</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-86.41</t>
+          <t>-0.864067141257275</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>-87.61</t>
+          <t>-0.876095471263763</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>-88.21</t>
+          <t>-0.88205230447677</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>-90.04</t>
+          <t>-0.900427993532121</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>-90.59</t>
+          <t>-0.905894969013121</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>-88.62</t>
+          <t>-0.886211632175973</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>-87.81</t>
+          <t>-0.878079404073111</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>-81.72</t>
+          <t>-0.817230029112699</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Estônia</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1727,84 +1732,84 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>255.15</t>
+          <t>2.55151984783146</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>231.57</t>
+          <t>2.315669429511</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>397.55</t>
+          <t>3.9754802203682</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>366.61</t>
+          <t>3.66612525909107</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-28.77</t>
+          <t>-0.287711036865561</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-76.26</t>
+          <t>-0.762636881224698</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-77.42</t>
+          <t>-0.774160934928728</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-82.95</t>
+          <t>-0.829524928795314</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>-89.3</t>
+          <t>-0.893020476350602</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>-82.29</t>
+          <t>-0.822928956792168</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>-71.65</t>
+          <t>-0.716522940859596</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>-80.3</t>
+          <t>-0.803001224390846</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>-83.31</t>
+          <t>-0.833083752366047</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>-83.64</t>
+          <t>-0.836425479720775</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>-76.81</t>
+          <t>-0.768134695142617</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Finlândia</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1814,84 +1819,84 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-78.42</t>
+          <t>-0.784189903250359</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>-78.98</t>
+          <t>-0.789775704432916</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>-70.2</t>
+          <t>-0.701964559508912</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>-73.64</t>
+          <t>-0.736426565722154</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-80.44</t>
+          <t>-0.804432387535403</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-83.66</t>
+          <t>-0.836574776276768</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-85.84</t>
+          <t>-0.858370997101782</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-86.16</t>
+          <t>-0.861584527562788</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>-89.35</t>
+          <t>-0.893539273579613</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>-89.67</t>
+          <t>-0.896689081548472</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>-90.24</t>
+          <t>-0.902415258141156</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>-90.55</t>
+          <t>-0.905516746174387</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>-88.52</t>
+          <t>-0.885235784640732</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>-88.18</t>
+          <t>-0.881833958439946</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>-82.25</t>
+          <t>-0.822542333406715</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>França</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1901,84 +1906,84 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-88.31</t>
+          <t>-0.88310548867318</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>-87.42</t>
+          <t>-0.874178689314158</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>-84.49</t>
+          <t>-0.844901118095248</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>-85.14</t>
+          <t>-0.8514433587241</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-88.98</t>
+          <t>-0.889774059206124</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-92.21</t>
+          <t>-0.922113155005674</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-92.74</t>
+          <t>-0.927379726159771</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-93.11</t>
+          <t>-0.931087344086571</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>-93.97</t>
+          <t>-0.939676014208769</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>-94.24</t>
+          <t>-0.942412277074755</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>-95.24</t>
+          <t>-0.952386614786361</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>-95.27</t>
+          <t>-0.952670631740228</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>-94.2</t>
+          <t>-0.942035293562635</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>-93.83</t>
+          <t>-0.938332790590514</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>-90.94</t>
+          <t>-0.909369131191822</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Reino Unido</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1988,84 +1993,84 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-87.14</t>
+          <t>-0.871439237489159</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>-86.48</t>
+          <t>-0.864772474868434</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>-81.56</t>
+          <t>-0.815554519163629</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>-82.94</t>
+          <t>-0.829401205008988</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-87.25</t>
+          <t>-0.872465575297263</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-90.5</t>
+          <t>-0.904981596199183</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-91.4</t>
+          <t>-0.913952268219918</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-91.44</t>
+          <t>-0.914438975735946</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>-92.31</t>
+          <t>-0.923144991734395</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>-92.58</t>
+          <t>-0.925801194237629</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>-93.52</t>
+          <t>-0.935160483616723</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>-93.91</t>
+          <t>-0.939143884318997</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>-93.25</t>
+          <t>-0.932504308528908</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>-92.51</t>
+          <t>-0.925149989459301</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>-90.09</t>
+          <t>-0.900878712737737</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Grécia</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2075,84 +2080,84 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-37.73</t>
+          <t>-0.377326674764476</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>-43.16</t>
+          <t>-0.43163944755415</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>-23.9</t>
+          <t>-0.238989679412458</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>-32.08</t>
+          <t>-0.320804574867693</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-50.61</t>
+          <t>-0.506134674182293</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-72.34</t>
+          <t>-0.723353703407146</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-76.41</t>
+          <t>-0.764088616781327</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-78.62</t>
+          <t>-0.786219183298239</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>-82.18</t>
+          <t>-0.821766977985073</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>-79.55</t>
+          <t>-0.795549645646338</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>-85.61</t>
+          <t>-0.856112123586877</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>-88.13</t>
+          <t>-0.88129881528934</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>-85.72</t>
+          <t>-0.857157210799548</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>-85.05</t>
+          <t>-0.850529754376181</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>-78.4</t>
+          <t>-0.784026612986282</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Hungria</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2162,84 +2167,84 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>-36.83</t>
+          <t>-0.368349651064327</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>-29.48</t>
+          <t>-0.294818358543498</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>-4.44</t>
+          <t>-0.0444007439876726</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>-25.47</t>
+          <t>-0.254672985914233</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-45.48</t>
+          <t>-0.454779246617387</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>-50.27</t>
+          <t>-0.502683796473014</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>-61.51</t>
+          <t>-0.615106608311433</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>-61.01</t>
+          <t>-0.610135585635334</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>-68.55</t>
+          <t>-0.685463270905021</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>-68.63</t>
+          <t>-0.686260918493008</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>-70.61</t>
+          <t>-0.706123688540201</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>-68.45</t>
+          <t>-0.684468743594963</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>-65.59</t>
+          <t>-0.655852906815175</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>-52.42</t>
+          <t>-0.52424976472579</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>-16.57</t>
+          <t>-0.165745414481238</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Indonésia</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2249,84 +2254,84 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>201.59</t>
+          <t>2.01585216261486</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>198.12</t>
+          <t>1.98123786367214</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>216.48</t>
+          <t>2.16481207732489</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>252.87</t>
+          <t>2.52869141234306</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>145.37</t>
+          <t>1.45371485651098</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>58.71</t>
+          <t>0.587125222591029</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>47.84</t>
+          <t>0.4784279043557</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>41.89</t>
+          <t>0.418902844425382</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>28.43</t>
+          <t>0.284327087798015</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>26.22</t>
+          <t>0.262230858417599</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>14.97</t>
+          <t>0.149703470405867</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>9.28</t>
+          <t>0.0927852293604625</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>19.31</t>
+          <t>0.193083401305918</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>14.1</t>
+          <t>0.141029131260669</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>46.69</t>
+          <t>0.46693141940597</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Índia</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2336,84 +2341,84 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>161.68</t>
+          <t>1.61680659089177</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>181.99</t>
+          <t>1.81992146869379</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>173.7</t>
+          <t>1.73702781847773</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>173.01</t>
+          <t>1.73005461243616</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>141.89</t>
+          <t>1.4189331200658</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>134.6</t>
+          <t>1.34600187707885</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>146</t>
+          <t>1.45996637747588</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>157.91</t>
+          <t>1.579050660947</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>170.53</t>
+          <t>1.70528494660569</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>174.83</t>
+          <t>1.74832985957407</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>174.73</t>
+          <t>1.74727076819458</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>177.7</t>
+          <t>1.77704288450908</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>188.34</t>
+          <t>1.8833753305281</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>207.44</t>
+          <t>2.07440075318266</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>219.94</t>
+          <t>2.19935385708411</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Irlanda</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2423,84 +2428,84 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>-72.88</t>
+          <t>-0.728782330895923</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>-69.97</t>
+          <t>-0.699658083851179</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>-75.71</t>
+          <t>-0.757115741174333</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>-76.85</t>
+          <t>-0.768451997438769</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-79.99</t>
+          <t>-0.799927093141315</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>-84.13</t>
+          <t>-0.84133672331979</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>-83.99</t>
+          <t>-0.839910525329552</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>-84.7</t>
+          <t>-0.846981083159322</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>-87.49</t>
+          <t>-0.874871222709913</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>-89.44</t>
+          <t>-0.894382011754432</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>-91.72</t>
+          <t>-0.917237053839825</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>-92.31</t>
+          <t>-0.923071532156494</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>-91.53</t>
+          <t>-0.915262545239419</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>-90.17</t>
+          <t>-0.901662294261529</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>-89.49</t>
+          <t>-0.894865943674478</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Itália</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2510,84 +2515,84 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>-69.94</t>
+          <t>-0.699436556798549</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>-69.91</t>
+          <t>-0.699063920053534</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>-64.16</t>
+          <t>-0.641569918745747</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>-64.49</t>
+          <t>-0.644867995654458</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-73.45</t>
+          <t>-0.734480684131056</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>-81.08</t>
+          <t>-0.810812408883341</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>-82.38</t>
+          <t>-0.823803019355811</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>-82.75</t>
+          <t>-0.827488815663236</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>-83.06</t>
+          <t>-0.830601610765229</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>-84.15</t>
+          <t>-0.841527987167906</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>-86.91</t>
+          <t>-0.869069307547288</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>-88.3</t>
+          <t>-0.883026129201482</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>-85.87</t>
+          <t>-0.858711557048345</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>-85.76</t>
+          <t>-0.857647457380663</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>-79.86</t>
+          <t>-0.798595459125932</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Japão</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2597,84 +2602,84 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>-70.81</t>
+          <t>-0.708116169686011</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>-71.02</t>
+          <t>-0.71022921667977</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>-63.99</t>
+          <t>-0.639872011883236</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>-60.66</t>
+          <t>-0.60663985534466</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-73.33</t>
+          <t>-0.733259298810985</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>-79.8</t>
+          <t>-0.797968362710372</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>-80.91</t>
+          <t>-0.80911993975806</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>-81.27</t>
+          <t>-0.812666171680097</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>-83.36</t>
+          <t>-0.833575030984449</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>-84.18</t>
+          <t>-0.841836459571746</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>-86.28</t>
+          <t>-0.862753258061278</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>-86.14</t>
+          <t>-0.861374657128403</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>-82.51</t>
+          <t>-0.825058255624955</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>-83.72</t>
+          <t>-0.837245758089199</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>-77.51</t>
+          <t>-0.775094552121142</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Coreia do Sul</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2684,84 +2689,84 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>-67</t>
+          <t>-0.670042057408543</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>-67.74</t>
+          <t>-0.677410927303489</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>-65.8</t>
+          <t>-0.657991134989022</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>-58.41</t>
+          <t>-0.584069260331234</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-72.17</t>
+          <t>-0.721726531788071</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>-82.69</t>
+          <t>-0.826918012230953</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>-82.62</t>
+          <t>-0.82620953124743</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>-79.81</t>
+          <t>-0.798088022367337</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>-82</t>
+          <t>-0.820049034100546</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>-81.02</t>
+          <t>-0.810210015113262</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>-84.36</t>
+          <t>-0.843550689794872</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>-85.23</t>
+          <t>-0.852306382282748</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>-82.07</t>
+          <t>-0.82068516508674</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>-81.84</t>
+          <t>-0.818379508999457</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>-73.66</t>
+          <t>-0.736550873502196</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Lituânia</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2771,84 +2776,84 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>-42.12</t>
+          <t>-0.421152805926357</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>-58.75</t>
+          <t>-0.587453672592332</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>-60.59</t>
+          <t>-0.605874501911557</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>-53.96</t>
+          <t>-0.53964666720329</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-59.66</t>
+          <t>-0.596630589959468</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>-64.36</t>
+          <t>-0.643556097015704</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>-77.11</t>
+          <t>-0.771142437816334</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>-72.26</t>
+          <t>-0.722606228033125</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>-76.86</t>
+          <t>-0.76862239473224</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>-82.43</t>
+          <t>-0.824303177871681</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>-85.15</t>
+          <t>-0.851476413708514</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>-85.12</t>
+          <t>-0.85119117891802</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>-89.58</t>
+          <t>-0.895797074674453</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>-86.74</t>
+          <t>-0.867399530023146</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>-70.66</t>
+          <t>-0.706574329519026</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Luxemburgo</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2858,84 +2863,84 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>-76.28</t>
+          <t>-0.762759595948242</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>-84.13</t>
+          <t>-0.841253111226861</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>-82.03</t>
+          <t>-0.820250745855761</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>-83.75</t>
+          <t>-0.837450574292253</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-87.48</t>
+          <t>-0.874752803876036</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>-91.45</t>
+          <t>-0.914486808870655</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>-91.74</t>
+          <t>-0.917374147854292</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>-90.59</t>
+          <t>-0.905941254265202</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>-91.92</t>
+          <t>-0.919166459653279</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>-91.38</t>
+          <t>-0.913766399800747</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>-93.05</t>
+          <t>-0.93045504231474</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>-92.96</t>
+          <t>-0.929638613050203</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>-91.58</t>
+          <t>-0.915844126799954</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>-90.72</t>
+          <t>-0.907245395523832</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>-89.46</t>
+          <t>-0.894575123071322</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Letônia</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2945,84 +2950,84 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>6.08</t>
+          <t>0.0608070670224024</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>-4.98</t>
+          <t>-0.0498257498853024</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>6.68</t>
+          <t>0.0668144748247781</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>-13.85</t>
+          <t>-0.138535080528898</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-28.61</t>
+          <t>-0.286139704552105</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>-37.96</t>
+          <t>-0.37962243447633</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>-56.84</t>
+          <t>-0.568447454097967</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>-51.48</t>
+          <t>-0.51482215595593</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>-42.44</t>
+          <t>-0.424443870492546</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>39.66</t>
+          <t>0.396559138792151</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>554.65</t>
+          <t>5.54648496068712</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>166.58</t>
+          <t>1.66580673497431</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>-75.29</t>
+          <t>-0.752930822861459</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>-73.94</t>
+          <t>-0.739385469948717</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>-61.41</t>
+          <t>-0.614128633437031</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3032,84 +3037,84 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>250.67</t>
+          <t>2.50665547309961</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>261.65</t>
+          <t>2.61654252991656</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>278.24</t>
+          <t>2.78243337347184</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>211.38</t>
+          <t>2.11383682567497</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>145.6</t>
+          <t>1.45595532102217</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>77.18</t>
+          <t>0.771756081558392</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>0.409981981807184</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>40.3</t>
+          <t>0.403031495666292</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>54.15</t>
+          <t>0.541532001421436</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>68.33</t>
+          <t>0.683311950071009</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>46.31</t>
+          <t>0.463111823663357</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>45.23</t>
+          <t>0.452310326369413</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>66.97</t>
+          <t>0.669722004319989</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>101.01</t>
+          <t>1.01011969262783</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>188.93</t>
+          <t>1.88929103225194</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3119,84 +3124,84 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>39.78</t>
+          <t>0.397760069994671</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>17.29</t>
+          <t>0.172937018538225</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>158.26</t>
+          <t>1.58255815142108</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>54.22</t>
+          <t>0.542225954197174</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>3.56</t>
+          <t>0.0356471359852502</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>-14.66</t>
+          <t>-0.146608665358656</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>-52.16</t>
+          <t>-0.521556804812164</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>-49.34</t>
+          <t>-0.493381947561077</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>-53.55</t>
+          <t>-0.535508914408002</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>-43.51</t>
+          <t>-0.435082593528122</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>-38.74</t>
+          <t>-0.387358366276398</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>-44.53</t>
+          <t>-0.445315624958443</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>-27.47</t>
+          <t>-0.274735283644091</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>-14.46</t>
+          <t>-0.144636132145851</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>17.07</t>
+          <t>0.170710551313173</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Países Baixos</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3206,84 +3211,84 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>-92.33</t>
+          <t>-0.923300440375201</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>-92.4</t>
+          <t>-0.923983407619516</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>-88.3</t>
+          <t>-0.882982560550839</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>-90.95</t>
+          <t>-0.909498931249948</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-92.51</t>
+          <t>-0.925139077605774</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>-93.94</t>
+          <t>-0.939357442494932</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>-93.92</t>
+          <t>-0.939199750760581</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>-93.77</t>
+          <t>-0.937719853960894</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>-94.67</t>
+          <t>-0.946667461295828</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>-94.68</t>
+          <t>-0.946836386638834</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>-95.36</t>
+          <t>-0.95362451823415</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>-95.3</t>
+          <t>-0.953017369679503</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>-94.59</t>
+          <t>-0.945862463152916</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>-94.3</t>
+          <t>-0.943009538038654</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>-92.62</t>
+          <t>-0.926232689370009</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Polônia</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3293,84 +3298,84 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>-24.33</t>
+          <t>-0.24327878254384</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>-33.01</t>
+          <t>-0.330074559787869</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>-20.23</t>
+          <t>-0.202277527242285</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>-39.1</t>
+          <t>-0.390954256479066</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-44.78</t>
+          <t>-0.447776825003974</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>-55.35</t>
+          <t>-0.553478485456849</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>-45.02</t>
+          <t>-0.450190687044043</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>-43.12</t>
+          <t>-0.43119569226563</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>-42.91</t>
+          <t>-0.42908823834393</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>-46.65</t>
+          <t>-0.466492880525225</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>-48.6</t>
+          <t>-0.486026952258068</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>-50.35</t>
+          <t>-0.503468777726796</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>-50.15</t>
+          <t>-0.501455577753556</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>-50.21</t>
+          <t>-0.502083422396211</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>-38.46</t>
+          <t>-0.384576414388948</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3380,84 +3385,84 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>-56.16</t>
+          <t>-0.56163309444923</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>-57.05</t>
+          <t>-0.570488430349601</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>-44.13</t>
+          <t>-0.441280282589298</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>-50.52</t>
+          <t>-0.505196443530217</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-62.96</t>
+          <t>-0.629550073394165</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>-76.48</t>
+          <t>-0.764790916165478</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>-77.27</t>
+          <t>-0.772732785125958</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>-76.85</t>
+          <t>-0.768482216837571</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>-79.44</t>
+          <t>-0.794405665651216</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>-81.21</t>
+          <t>-0.812093916676869</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>-85.31</t>
+          <t>-0.853074721280055</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>-86.2</t>
+          <t>-0.862044500716962</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>-84.98</t>
+          <t>-0.849841227092393</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>-85.7</t>
+          <t>-0.856970156035569</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>-75.67</t>
+          <t>-0.756664526218786</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Romênia</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3467,84 +3472,84 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>100.21</t>
+          <t>1.00211460528191</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>97.32</t>
+          <t>0.973230674311266</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>145.57</t>
+          <t>1.45566953783599</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>82.31</t>
+          <t>0.823078095889341</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>111.64</t>
+          <t>1.11641065341251</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>0.460041446097677</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>21.81</t>
+          <t>0.218138769814948</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>18.79</t>
+          <t>0.187854124684752</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>0.0122497109841213</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>40.03</t>
+          <t>0.40025293510285</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>-8.37</t>
+          <t>-0.0836835368411152</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>-17.94</t>
+          <t>-0.179437408305449</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>-63.08</t>
+          <t>-0.63077903849243</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>-68.07</t>
+          <t>-0.680725091074047</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>-42.33</t>
+          <t>-0.423315322001229</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Rússia</t>
+          <t>43</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3554,84 +3559,84 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>105.36</t>
+          <t>1.0535969656429</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>72.82</t>
+          <t>0.728225957079937</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>103.19</t>
+          <t>1.03186248869471</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>98.89</t>
+          <t>0.988872655983282</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>113.46</t>
+          <t>1.13460645118562</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>51.69</t>
+          <t>0.516855048644261</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>42.77</t>
+          <t>0.427740641296227</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>32.53</t>
+          <t>0.325286718654827</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>17.51</t>
+          <t>0.17514668362803</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>29.54</t>
+          <t>0.295407488867688</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>20.98</t>
+          <t>0.209751437354058</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>12.69</t>
+          <t>0.12689338777299</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>6.46</t>
+          <t>0.0645711315780086</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>-2.74</t>
+          <t>-0.0274159236984566</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>25.2</t>
+          <t>0.251985701335241</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Eslováquia</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3641,84 +3646,84 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>7.94</t>
+          <t>0.0794000770367251</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>10.71</t>
+          <t>0.107082380445747</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>15.01</t>
+          <t>0.150148706023907</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>-14.16</t>
+          <t>-0.141606531357646</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-18.09</t>
+          <t>-0.180924410471418</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>-45.48</t>
+          <t>-0.454821408989345</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>-52.39</t>
+          <t>-0.523872882199641</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>-53.38</t>
+          <t>-0.533822610931959</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>-62.45</t>
+          <t>-0.624547279619119</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>-74.87</t>
+          <t>-0.748728114364065</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>-77.61</t>
+          <t>-0.776135211223504</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>-77.8</t>
+          <t>-0.777975674147515</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>-79.86</t>
+          <t>-0.798645861623328</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>-74.05</t>
+          <t>-0.740515065710468</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>-71.75</t>
+          <t>-0.717513257247486</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Eslovênia</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3728,84 +3733,84 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>-86.76</t>
+          <t>-0.867570538329067</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>-86.22</t>
+          <t>-0.862185070816408</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>-82.01</t>
+          <t>-0.820114189095289</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>-82.49</t>
+          <t>-0.824857501689033</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-86.91</t>
+          <t>-0.869060281661968</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>-89.94</t>
+          <t>-0.899370726186986</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>-90.25</t>
+          <t>-0.90245675913781</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>-90.56</t>
+          <t>-0.905587080844938</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>-91.97</t>
+          <t>-0.919653788161717</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>-92.32</t>
+          <t>-0.923205897240087</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>-93.23</t>
+          <t>-0.93232537636779</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>-93.29</t>
+          <t>-0.932930639124978</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>-92.16</t>
+          <t>-0.921642345823718</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>-93.87</t>
+          <t>-0.938739696287131</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>-91.33</t>
+          <t>-0.913257991941257</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Suécia</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3815,84 +3820,84 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>-89.81</t>
+          <t>-0.89805462613026</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>-89.76</t>
+          <t>-0.897634719939046</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>-87.16</t>
+          <t>-0.871630651824366</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>-88.35</t>
+          <t>-0.883479883110791</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-90.7</t>
+          <t>-0.907033774434369</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>-93.28</t>
+          <t>-0.932795540052151</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>-93.55</t>
+          <t>-0.935538009011835</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>-93.41</t>
+          <t>-0.934084782446458</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>-94.52</t>
+          <t>-0.945205439246915</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>-94.47</t>
+          <t>-0.944720707415311</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>-95.05</t>
+          <t>-0.950495399787848</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>-94.58</t>
+          <t>-0.945802220950584</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>-94.05</t>
+          <t>-0.940505049986884</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>-92.97</t>
+          <t>-0.929656772092927</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>-90.48</t>
+          <t>-0.904787518659924</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Turquia</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3902,84 +3907,84 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>39.38</t>
+          <t>0.39383411753242</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>20.53</t>
+          <t>0.205347955042005</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>-2.78</t>
+          <t>-0.0278080296331312</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>-7.34</t>
+          <t>-0.073381104080675</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-31.45</t>
+          <t>-0.314461957576255</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>-42.73</t>
+          <t>-0.427283679247913</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>-17.22</t>
+          <t>-0.172209649729386</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>42.2</t>
+          <t>0.421983745157813</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>40.4</t>
+          <t>0.403991686550524</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>51.85</t>
+          <t>0.518483455495208</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>35.25</t>
+          <t>0.352482826259312</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>42.76</t>
+          <t>0.427617181577287</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>57.9</t>
+          <t>0.578973534337397</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>55.09</t>
+          <t>0.550863016407221</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>167.26</t>
+          <t>1.6725635414605</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>China: Taiwan</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3989,84 +3994,84 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>-76.43</t>
+          <t>-0.76425162512627</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>-77.7</t>
+          <t>-0.776960206138772</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>-73.39</t>
+          <t>-0.733855606440929</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>-74.54</t>
+          <t>-0.745439946952072</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>-81.62</t>
+          <t>-0.816225564790871</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>-86.91</t>
+          <t>-0.869075003526944</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>-86.57</t>
+          <t>-0.865708017095591</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>-87.85</t>
+          <t>-0.878514675242851</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>-87.96</t>
+          <t>-0.87957177384605</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>-86.73</t>
+          <t>-0.867305097589954</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>-87.1</t>
+          <t>-0.871028909550987</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>-85.88</t>
+          <t>-0.85882102948589</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>-80.5</t>
+          <t>-0.804986973391135</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>-79.16</t>
+          <t>-0.791568976290118</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>-69.37</t>
+          <t>-0.693656226088707</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4076,84 +4081,84 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>-77.24</t>
+          <t>-0.772408824969916</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>-75.21</t>
+          <t>-0.752124608051285</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>-73.45</t>
+          <t>-0.734482161012319</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>-75.59</t>
+          <t>-0.755944155303677</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-78.6</t>
+          <t>-0.786010873998558</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>-85.97</t>
+          <t>-0.859731405481571</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>-85.95</t>
+          <t>-0.85952395898072</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>-85.21</t>
+          <t>-0.852089872486373</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>-85.13</t>
+          <t>-0.851325782401734</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>-86.97</t>
+          <t>-0.869693214525948</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>-88.63</t>
+          <t>-0.88631276919673</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>-88.21</t>
+          <t>-0.882059810101902</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>-86.64</t>
+          <t>-0.866405279370589</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>-86.19</t>
+          <t>-0.861942010101747</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>-79.36</t>
+          <t>-0.793556486931718</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Resto do mundo</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4163,84 +4168,84 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>722.05</t>
+          <t>7.22049875641498</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>682.74</t>
+          <t>6.82737833927024</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>624.45</t>
+          <t>6.24453046450377</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>662.97</t>
+          <t>6.62968094868721</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>684.35</t>
+          <t>6.84352183175753</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>637.27</t>
+          <t>6.37267191074989</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>632.1</t>
+          <t>6.32099310534395</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>634.95</t>
+          <t>6.3495206540563</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>646.86</t>
+          <t>6.46858826544252</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>619.61</t>
+          <t>6.19614630741322</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>625.67</t>
+          <t>6.25667895602122</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>613.34</t>
+          <t>6.13342458873582</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>637.22</t>
+          <t>6.3722379754772</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>570.65</t>
+          <t>5.70651807322249</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>550.97</t>
+          <t>5.5097059600219</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Mundo</t>
+          <t>46</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4250,84 +4255,84 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>394.17</t>
+          <t>3.94168614180507</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>370.93</t>
+          <t>3.70933932421029</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>375.26</t>
+          <t>3.75257073817262</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>399.53</t>
+          <t>3.99530960495908</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>394.47</t>
+          <t>3.94465408084421</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>342.19</t>
+          <t>3.42191151607244</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>335.34</t>
+          <t>3.35338377439859</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>329.42</t>
+          <t>3.2942052426148</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>331.72</t>
+          <t>3.31721803391992</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>301.77</t>
+          <t>3.01770196971507</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>284.57</t>
+          <t>2.8457304767631</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>270.18</t>
+          <t>2.70179342457073</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>276.4</t>
+          <t>2.76398281680864</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>245.22</t>
+          <t>2.45224258527784</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>276.13</t>
+          <t>2.76134623402282</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Croácia</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4339,7 +4344,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Suíça</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4351,7 +4356,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Noruega</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4363,7 +4368,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Africa do Sul</t>
+          <t>45</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4375,7 +4380,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Resto do mundo - Asia</t>
+          <t>47</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4387,7 +4392,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Resto do mundo - America</t>
+          <t>50</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4399,7 +4404,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Resto do mundo - Europa</t>
+          <t>48</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4411,7 +4416,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Resto do mundo - Africa</t>
+          <t>49</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4423,7 +4428,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Resto do mundo - Oriente Medio</t>
+          <t>51</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4470,6 +4475,11 @@
           <t>surplus_value.empe.r.pc</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4504,6 +4514,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Ochoa 2</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>rpO2</t>
